--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104657_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104657_W23.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7581</v>
+        <v>4.0748</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6185</v>
+        <v>2.1917</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1396</v>
+        <v>1.8831</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.8638</v>
+        <v>-0.8599</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0664</v>
+        <v>0.0634</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9302</v>
+        <v>-0.9233</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7829</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6238</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6467</v>
+        <v>-1.6326</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3536</v>
+        <v>0.6584</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2571</v>
+        <v>0.3295</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6106</v>
+        <v>0.3289</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>A. REYES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6544</v>
+        <v>2.9402</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9642</v>
+        <v>1.4929</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6902</v>
+        <v>1.4472</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6545</v>
+        <v>3.3191</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4356</v>
+        <v>-0.4225</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7811</v>
+        <v>3.7416</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.7538</v>
+        <v>4.2459</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.9852</v>
+        <v>-0.5795</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2315</v>
+        <v>4.8255</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0992</v>
+        <v>-0.9268</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5496</v>
+        <v>0.157</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4504</v>
+        <v>-1.0838</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-4.7803</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4537</v>
+        <v>3.6421</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2182</v>
+        <v>1.2438</v>
       </c>
       <c r="T3" t="n">
-        <v>3.7594</v>
+        <v>0.9378</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4588</v>
+        <v>0.306</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7712</v>
+        <v>-0.4846</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3214</v>
+        <v>-1.5741</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4525</v>
+        <v>2.5109</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9064</v>
+        <v>1.0675</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5461</v>
+        <v>1.4434</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7742</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.329</v>
+        <v>0.3275</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4452</v>
+        <v>0.4532</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0773</v>
+        <v>1.0658</v>
       </c>
       <c r="K4" t="n">
-        <v>0.928</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.303</v>
+        <v>-0.2851</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>2.2907</v>
+        <v>1.3448</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8026</v>
+        <v>0.9822</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4881</v>
+        <v>0.3627</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. REYES</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1341</v>
+        <v>1.3178</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2947</v>
+        <v>0.8205</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4288</v>
+        <v>0.4972</v>
       </c>
       <c r="G5" t="n">
-        <v>3.319</v>
+        <v>-0.6559</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4287</v>
+        <v>-1.4442</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7477</v>
+        <v>0.7883</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2774</v>
+        <v>-0.7749</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5683</v>
+        <v>-2.0037</v>
       </c>
       <c r="L5" t="n">
-        <v>4.8458</v>
+        <v>1.2288</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9584</v>
+        <v>0.119</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1397</v>
+        <v>0.5595</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0981</v>
+        <v>-0.4405</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.7635</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6293</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5622</v>
+        <v>1.8826</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9013</v>
+        <v>1.6441</v>
       </c>
       <c r="U5" t="n">
-        <v>0.339</v>
+        <v>0.2385</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4885</v>
+        <v>0.7739</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5812</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9751</v>
+        <v>0.7984</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6143</v>
+        <v>0.5905</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3609</v>
+        <v>0.2079</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.191</v>
+        <v>-1.1859</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.1053</v>
+        <v>-2.1052</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9143</v>
+        <v>0.9193</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7657</v>
+        <v>-0.7866</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2854</v>
+        <v>-1.3002</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4252</v>
+        <v>-0.3993</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>1.7772</v>
+        <v>1.6166</v>
       </c>
       <c r="T6" t="n">
-        <v>1.612</v>
+        <v>1.6417</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1651</v>
+        <v>-0.0251</v>
       </c>
       <c r="V6" t="n">
-        <v>3.1109</v>
+        <v>3.0993</v>
       </c>
       <c r="W6" t="n">
-        <v>4.5314</v>
+        <v>4.5157</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4205</v>
+        <v>-1.4163</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0471</v>
+        <v>0.0165</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9494</v>
+        <v>-1.8473</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9024</v>
+        <v>1.8638</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8182</v>
+        <v>-1.8276</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8049</v>
+        <v>-1.8173</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0133</v>
+        <v>-0.0103</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3579</v>
+        <v>-1.3847</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.206</v>
+        <v>-1.228</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4603</v>
+        <v>-0.443</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S7" t="n">
-        <v>0.291</v>
+        <v>0.3692</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4234</v>
+        <v>0.5664</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1325</v>
+        <v>-0.1972</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4619</v>
+        <v>-0.6157</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1608</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6227</v>
+        <v>-0.5472</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.5973000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1023</v>
+        <v>-1.1083</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5091</v>
+        <v>0.511</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6869</v>
+        <v>-0.6974</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7242</v>
+        <v>-0.7347</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.1002</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3781</v>
+        <v>-0.3736</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>0.323</v>
+        <v>0.1718</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7531</v>
+        <v>0.5411</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4301</v>
+        <v>-0.3692</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.099</v>
+        <v>-1.1008</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4205</v>
+        <v>-1.4163</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6444</v>
+        <v>-1.9308</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7348</v>
+        <v>-3.2794</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0904</v>
+        <v>1.3486</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.0849</v>
+        <v>-4.0915</v>
       </c>
       <c r="H9" t="n">
-        <v>0.404</v>
+        <v>0.4076</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.4888</v>
+        <v>-4.4991</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7292</v>
+        <v>-2.7618</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7202</v>
+        <v>0.71</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.4494</v>
+        <v>-3.4718</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3557</v>
+        <v>-1.3296</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0463</v>
+        <v>0.7559</v>
       </c>
       <c r="T9" t="n">
-        <v>0.741</v>
+        <v>1.2352</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6947</v>
+        <v>-0.4793</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8741</v>
+        <v>-0.8716</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.4885</v>
+        <v>-0.4846</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3141</v>
+        <v>-2.1296</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9296</v>
+        <v>-1.9737</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3846</v>
+        <v>-0.1559</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0287</v>
+        <v>-2.0501</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9865</v>
+        <v>-1.0151</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0422</v>
+        <v>-1.035</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3744</v>
+        <v>-0.4191</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3716</v>
+        <v>-0.4114</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0027</v>
+        <v>-0.0077</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6543</v>
+        <v>-1.631</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>3.8562</v>
+        <v>3.8697</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8486</v>
+        <v>0.3483</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4476</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4011</v>
+        <v>-0.2157</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.2148</v>
+        <v>-3.7662</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7506</v>
+        <v>-3.7093</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4641</v>
+        <v>-0.0569</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.897</v>
+        <v>-1.9133</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.753</v>
+        <v>-1.7656</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.144</v>
+        <v>-0.1476</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5085</v>
+        <v>-1.5441</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2867</v>
+        <v>-2.3107</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3885</v>
+        <v>-0.3692</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.283</v>
+        <v>0.1765</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.747</v>
+        <v>0.3388</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5359</v>
+        <v>-0.1623</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.5812</v>
+        <v>-1.5741</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5812</v>
+        <v>-1.5741</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.6662</v>
+        <v>-6.1581</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.336</v>
+        <v>-2.9114</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.3302</v>
+        <v>-3.2467</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8916</v>
+        <v>-3.9012</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.5264</v>
+        <v>-3.5378</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3652</v>
+        <v>-0.3634</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6767</v>
+        <v>-2.6974</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.4874</v>
+        <v>-2.5036</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2149</v>
+        <v>-1.2037</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.039</v>
+        <v>-1.0342</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0429</v>
+        <v>0.4667</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4748</v>
+        <v>0.9242</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5178</v>
+        <v>-0.4575</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3743</v>
+        <v>-2.9418</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.730900000000002</v>
+        <v>-7.6265</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3568</v>
+        <v>4.6845</v>
       </c>
       <c r="G13" t="n">
-        <v>-12.9297</v>
+        <v>-12.9829</v>
       </c>
       <c r="H13" t="n">
-        <v>-12.3433</v>
+        <v>-12.4175</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5863000000000004</v>
+        <v>-0.5653000000000002</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.7155</v>
+        <v>-4.9816</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.632999999999999</v>
+        <v>-8.821200000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9177</v>
+        <v>3.8395</v>
       </c>
       <c r="M13" t="n">
-        <v>-8.2141</v>
+        <v>-8.001100000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.7102</v>
+        <v>-3.5962</v>
       </c>
       <c r="O13" t="n">
-        <v>-4.504100000000001</v>
+        <v>-4.404800000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4023</v>
+        <v>3.4142</v>
       </c>
       <c r="Q13" t="n">
-        <v>-21.5492</v>
+        <v>-21.6251</v>
       </c>
       <c r="R13" t="n">
-        <v>24.9518</v>
+        <v>25.0395</v>
       </c>
       <c r="S13" t="n">
-        <v>6.563299999999999</v>
+        <v>9.034599999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>7.2133</v>
+        <v>9.705</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6505000000000003</v>
+        <v>-0.6702</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.4102</v>
+        <v>-2.4083</v>
       </c>
       <c r="W13" t="n">
-        <v>9.3201</v>
+        <v>9.275499999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-11.7303</v>
+        <v>-11.6835</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.0478</v>
+        <v>11.4384</v>
       </c>
       <c r="E14" t="n">
-        <v>8.469799999999999</v>
+        <v>8.9634</v>
       </c>
       <c r="F14" t="n">
-        <v>1.578</v>
+        <v>2.475</v>
       </c>
       <c r="G14" t="n">
-        <v>7.6737</v>
+        <v>7.6574</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5844</v>
+        <v>4.5757</v>
       </c>
       <c r="I14" t="n">
-        <v>3.0893</v>
+        <v>3.0817</v>
       </c>
       <c r="J14" t="n">
-        <v>6.7471</v>
+        <v>6.6931</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5806</v>
+        <v>3.5433</v>
       </c>
       <c r="L14" t="n">
-        <v>3.1665</v>
+        <v>3.1498</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9266</v>
+        <v>0.9643</v>
       </c>
       <c r="N14" t="n">
-        <v>1.0038</v>
+        <v>1.0324</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R14" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.2746</v>
+        <v>-1.8453</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1644</v>
+        <v>-0.5742</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.1102</v>
+        <v>-1.2711</v>
       </c>
       <c r="V14" t="n">
-        <v>6.556</v>
+        <v>6.5368</v>
       </c>
       <c r="W14" t="n">
-        <v>7.4238</v>
+        <v>7.3971</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.1003</v>
+        <v>5.975</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1879</v>
+        <v>3.2593</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9124</v>
+        <v>2.7157</v>
       </c>
       <c r="G15" t="n">
-        <v>5.7155</v>
+        <v>5.719</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4743</v>
+        <v>2.4947</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2411</v>
+        <v>3.2243</v>
       </c>
       <c r="J15" t="n">
-        <v>4.922</v>
+        <v>4.8822</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0146</v>
+        <v>1.003</v>
       </c>
       <c r="L15" t="n">
-        <v>3.9074</v>
+        <v>3.8792</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7935</v>
+        <v>0.8368</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4598</v>
+        <v>1.4917</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9081</v>
+        <v>-1.0415</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0121</v>
+        <v>0.1087</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.896</v>
+        <v>-1.1502</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6419</v>
+        <v>2.8359</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2334</v>
+        <v>0.631</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4085</v>
+        <v>2.205</v>
       </c>
       <c r="G16" t="n">
-        <v>1.227</v>
+        <v>1.2459</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5899</v>
+        <v>0.6052</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6371</v>
+        <v>0.6407</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.0459</v>
+        <v>-0.0631</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.603</v>
+        <v>-0.614</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2729</v>
+        <v>1.309</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1929</v>
+        <v>1.2192</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6681</v>
+        <v>-0.5073</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2794</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.9475</v>
+        <v>-1.2014</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.0193</v>
+        <v>1.2721</v>
       </c>
       <c r="E17" t="n">
-        <v>1.066</v>
+        <v>1.1808</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0467</v>
+        <v>0.0914</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0328</v>
+        <v>-0.0218</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4443</v>
+        <v>0.4533</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4771</v>
+        <v>-0.4751</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1639</v>
+        <v>0.1634</v>
       </c>
       <c r="K17" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L17" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1967</v>
+        <v>-0.1852</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3923</v>
+        <v>0.4016</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4942</v>
+        <v>-0.2508</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1905</v>
+        <v>-0.0721</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3037</v>
+        <v>-0.1786</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.65</v>
+        <v>1.2364</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9692</v>
+        <v>-1.7434</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6192</v>
+        <v>2.9798</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3429</v>
+        <v>2.3488</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7964</v>
+        <v>1.8006</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5464</v>
+        <v>0.5483</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6288</v>
+        <v>0.6261</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5541</v>
+        <v>0.5516</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7141</v>
+        <v>1.7228</v>
       </c>
       <c r="N18" t="n">
-        <v>1.2423</v>
+        <v>1.249</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6248</v>
+        <v>-0.0441</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3297</v>
+        <v>-0.0931</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2952</v>
+        <v>0.049</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8235</v>
+        <v>-0.475</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4645</v>
+        <v>-0.715</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.359</v>
+        <v>0.24</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.979</v>
+        <v>-0.9686</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4067</v>
+        <v>1.4209</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.3857</v>
+        <v>-2.3895</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2574</v>
+        <v>-1.272</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9524</v>
+        <v>0.948</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.2098</v>
+        <v>-2.22</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2784</v>
+        <v>0.3033</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4542</v>
+        <v>0.4729</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7933</v>
+        <v>-0.4656</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6321</v>
+        <v>0.3992</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4254</v>
+        <v>-0.8648</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0632</v>
+        <v>-1.0291</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0291</v>
+        <v>-1.0327</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.034</v>
+        <v>0.0036</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6304</v>
+        <v>-0.6261</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1746</v>
+        <v>0.1752</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2477</v>
+        <v>0.2799</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0877</v>
+        <v>0.0882</v>
       </c>
       <c r="U20" t="n">
-        <v>0.16</v>
+        <v>0.1917</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2238</v>
+        <v>-1.8528</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1772</v>
+        <v>-0.6644</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.401</v>
+        <v>-1.1885</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8457</v>
+        <v>-1.8446</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.0056</v>
+        <v>-2.0102</v>
       </c>
       <c r="I21" t="n">
-        <v>0.16</v>
+        <v>0.1656</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3108</v>
+        <v>-1.3307</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0198</v>
+        <v>-2.0382</v>
       </c>
       <c r="L21" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.5139</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0142</v>
+        <v>0.028</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8072</v>
+        <v>0.1707</v>
       </c>
       <c r="T21" t="n">
-        <v>1.488</v>
+        <v>0.6663</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6808</v>
+        <v>-0.4956</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8317</v>
+        <v>-2.0261</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4302</v>
+        <v>-3.1921</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4015</v>
+        <v>1.166</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3893</v>
+        <v>-3.0237</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6318</v>
+        <v>0.6485</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2425</v>
+        <v>-3.6722</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3268</v>
+        <v>-2.869</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1775</v>
+        <v>0.1034</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1493</v>
+        <v>-2.9724</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0625</v>
+        <v>-0.1548</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4542</v>
+        <v>0.5451</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3918</v>
+        <v>-0.6998</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3137</v>
+        <v>0.4936</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6079</v>
+        <v>-0.3232</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2942</v>
+        <v>0.8168</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0192</v>
+        <v>-2.0264</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5324</v>
+        <v>-1.0996</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5133</v>
+        <v>-0.9267</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.0275</v>
+        <v>1.41</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6375999999999999</v>
+        <v>1.645</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.6652</v>
+        <v>-0.235</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.8549</v>
+        <v>1.3211</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1039</v>
+        <v>1.1721</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.9588</v>
+        <v>0.1489</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1726</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5337</v>
+        <v>0.4729</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7063</v>
+        <v>-0.384</v>
       </c>
       <c r="P23" t="n">
-        <v>1.5878</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5132</v>
+        <v>-0.5258</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6775</v>
+        <v>-0.2535</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1907</v>
+        <v>-0.2724</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2114</v>
+        <v>-3.2332</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.126</v>
+        <v>-2.595</v>
       </c>
       <c r="F24" t="n">
-        <v>3.9146</v>
+        <v>-0.6382</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5733</v>
+        <v>0.5051</v>
       </c>
       <c r="H24" t="n">
-        <v>0.264</v>
+        <v>0.3419</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3092</v>
+        <v>0.1632</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8027</v>
+        <v>0.6454</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9147</v>
+        <v>-0.2176</v>
       </c>
       <c r="L24" t="n">
-        <v>0.112</v>
+        <v>0.863</v>
       </c>
       <c r="M24" t="n">
-        <v>1.376</v>
+        <v>-0.1403</v>
       </c>
       <c r="N24" t="n">
-        <v>1.1787</v>
+        <v>0.5595</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1973</v>
+        <v>-0.6998</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.3098</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q24" t="n">
-        <v>-6.805</v>
+        <v>-4.5526</v>
       </c>
       <c r="R24" t="n">
-        <v>2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3644</v>
+        <v>0.2892</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1603</v>
+        <v>0.2228</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2041</v>
+        <v>0.0664</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3214</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9124</v>
+        <v>-3.5751</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.779</v>
+        <v>-7.519</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1334</v>
+        <v>3.9439</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5234</v>
+        <v>0.5815</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3449</v>
+        <v>0.2669</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1785</v>
+        <v>0.3145</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6801</v>
+        <v>-0.8126</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2047</v>
+        <v>-0.9243</v>
       </c>
       <c r="L25" t="n">
-        <v>0.8848</v>
+        <v>0.1117</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1567</v>
+        <v>1.3941</v>
       </c>
       <c r="N25" t="n">
-        <v>0.5496</v>
+        <v>1.1912</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7063</v>
+        <v>0.2028</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.8562</v>
+        <v>-4.325</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.5367</v>
+        <v>-6.8289</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>2.5039</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4189</v>
+        <v>0.0106</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0151</v>
+        <v>-0.193</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4038</v>
+        <v>0.2036</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>0.3155</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>5.374100000000002</v>
+        <v>8.540099999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.196100000000001</v>
+        <v>-4.5267</v>
       </c>
       <c r="F26" t="n">
-        <v>9.570400000000001</v>
+        <v>13.067</v>
       </c>
       <c r="G26" t="n">
-        <v>12.9297</v>
+        <v>12.9829</v>
       </c>
       <c r="H26" t="n">
-        <v>12.3433</v>
+        <v>12.4177</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5860999999999998</v>
+        <v>0.5653000000000005</v>
       </c>
       <c r="J26" t="n">
-        <v>8.2143</v>
+        <v>8.001100000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7102</v>
+        <v>3.596199999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>4.504000000000001</v>
+        <v>4.404800000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>4.7155</v>
+        <v>4.9817</v>
       </c>
       <c r="N26" t="n">
-        <v>8.633000000000001</v>
+        <v>8.821399999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.917800000000001</v>
+        <v>-3.839600000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.402499999999999</v>
+        <v>-3.414499999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-24.9517</v>
+        <v>-25.0394</v>
       </c>
       <c r="R26" t="n">
-        <v>21.5492</v>
+        <v>21.6249</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.563199999999999</v>
+        <v>-3.4364</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6502999999999999</v>
+        <v>0.6702000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-7.2136</v>
+        <v>-4.1066</v>
       </c>
       <c r="V26" t="n">
-        <v>2.410100000000001</v>
+        <v>2.407999999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>11.891</v>
+        <v>11.8413</v>
       </c>
       <c r="X26" t="n">
-        <v>-9.480900000000002</v>
+        <v>-9.433299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104657_W23.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104657_W23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.5741</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.4163</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.4163</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.4846</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.5741</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-11.6835</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104657_W23.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-9.433299999999999</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
